--- a/product_surveys/011_natural_overlay_feedback_form--product_surveys.xlsx
+++ b/product_surveys/011_natural_overlay_feedback_form--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Desktop'}</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'web'}</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Web'}</t>
+          <t>Web</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'it_was_difficult_to_find_where_to_click'}</t>
+          <t>it_was_difficult_to_find_where_to_click</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'It was difficult to find where to click'}</t>
+          <t>It was difficult to find where to click</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'it_was_difficult_to_understand_the_natural_overlay'}</t>
+          <t>it_was_difficult_to_understand_the_natural_overlay</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'It was difficult to understand the natural overlay'}</t>
+          <t>It was difficult to understand the natural overlay</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'it_was_a_minor_issue'}</t>
+          <t>it_was_a_minor_issue</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'It was a minor issue'}</t>
+          <t>It was a minor issue</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'increase_the_font_size'}</t>
+          <t>increase_the_font_size</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Increase the font size'}</t>
+          <t>Increase the font size</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'change_the_natural_overlay_to_always_be_on_top_of_other_apps'}</t>
+          <t>change_the_natural_overlay_to_always_be_on_top_of_other_apps</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Change the natural overlay to always be on top of other apps'}</t>
+          <t>Change the natural overlay to always be on top of other apps</t>
         </is>
       </c>
     </row>
